--- a/proposal_output/pathways_proposals.xlsx
+++ b/proposal_output/pathways_proposals.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Workflows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,19 +440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -540,17 +540,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8d40238686713191</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>training, ICT training, software development</t>
+          <t>training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The prequalification invites firms for ICT systems management, software licenses, e-learning systems, and training on ICT security.</t>
+          <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open categories are open to all eligible firms; reserved categories are restricted to AGPO registered groups (Youth, Women, PWDs).</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -609,22 +609,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f7683a8e4ad35977</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Climate Change AI Grant Calls</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/calls</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, funding opportunity, climate technology Africa funding</t>
+          <t>analysis, machine learning, training</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Offers grants and funding programs focusing on the intersection of climate change/climate tech and machine learning/artificial intelligence, including dedicated Africa research grants.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aims to support research, deployment, and dataset creation. Offers vary by call (some are closed or invitation-only, but new partnerships and calls are actively hosted on the platform).</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -680,22 +680,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17124d19bfc6b3cd</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/innovation_grants</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -710,27 +710,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, funding opportunity, grant application</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The program matches AI and machine learning keywords, but there are currently no active or planned future calls.</t>
+          <t>Matched configured ICT keyword(s): machine learning.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No future calls of this program are currently planned.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -748,8 +748,221 @@
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>17124d19bfc6b3cd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Climate Change AI Innovation Grants</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/innovation_grants</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>climatechange.ai</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analysis, machine learning, artificial intelligence, training</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>55b4d62ba31143e7</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>National Environment Management Authority</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analysis, analytical, training</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Matched configured ICT keyword(s): analysis, analytical, training.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3c2462dbed3db6a6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/news/bdn-certificationceremony</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>bluedot-network.org</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply for certification</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Matched configured ICT keyword(s): apply for certification.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O4"/>
+  <autoFilter ref="A1:O7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2415,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2537,12 +2750,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8d40238686713191</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2569,8 +2782,113 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>55b4d62ba31143e7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3c2462dbed3db6a6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/news/bdn-certificationceremony</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aa16da3072f3ff5b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/proposal_output/pathways_proposals.xlsx
+++ b/proposal_output/pathways_proposals.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -973,15 +973,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivia source links</t>
+          <t>Project owner source links</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1120,85 +1120,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Configure Tuesday/Thursday myGov alert recipient</t>
+          <t>Review new opportunities and assign a proposal owner</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Olivia / Technical owner</t>
+          <t>Project team</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SMTP access</t>
+          <t>Proposal tracker</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Set alert recipient and SMTP details in .env.</t>
+          <t>Update proposal status, owner, and notes after each scan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Review new opportunities and assign a proposal owner</t>
+          <t>Define content-folder approval and posting workflow</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Project team</t>
+          <t>Project owner / Content owner</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Proposal tracker</t>
+          <t>Content folder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Update proposal status, owner, and notes after each scan.</t>
+          <t>Confirm approval steps before connecting posting automation.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Define content-folder approval and posting workflow</t>
+          <t>Review performance and refine keywords</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Olivia / Content owner</t>
+          <t>Project team</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1207,50 +1207,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Content folder</t>
+          <t>Two weeks of results</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confirm approval steps before connecting posting automation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Review performance and refine keywords</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Project team</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Two weeks of results</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>Remove irrelevant results and add useful new terms.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1261,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1517,211 +1484,8 @@
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://example.gov/tenders</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://example.org/funding</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T10:04:59.643Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T10:11:01.745Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.bluedot-network.org/certification</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T16:20:04.680Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T18:24:37.612Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://le.ac.uk/study/international-students/countries/africa/kenya?utm_source=google-search&amp;utm_medium=paid&amp;utm_campaign=international-recruitment-2026&amp;utm_content=brand_ug-pg-ke&amp;gad_source=1&amp;gad_campaignid=22138204529&amp;gbraid=0AAAAA-Jv9mK-HMbYwd0xUiIwJsYXujvIu&amp;gclid=CjwKCAjw4dDTBhAqEiwAkHYmSix5GlL4etFz30Inndq4q0FUkb21c040s1XsfJ6nm0XAcefOUWDscRoCxsgQAvD_BwE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T19:52:46.857Z</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2899,11 +2663,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -2966,86 +2730,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>myGov alert</t>
+          <t>Proposal review</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tuesday/Thursday scheduler finds new matches</t>
+          <t>Workflow Queue contains Review required</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Send one email per new opportunity</t>
+          <t>Assess relevance and set bid decision</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Project team</t>
+          <t>Proposal owner</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Scheduler waits for SMTP configuration and prevents repeat alerts.</t>
+          <t>Update the workflow state using the command below.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Proposal review</t>
+          <t>Content publishing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workflow Queue contains Review required</t>
+          <t>Content receives approval</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assess relevance and set bid decision</t>
+          <t>Queue item for posting automation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Proposal owner</t>
+          <t>Content owner</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Update the workflow state using the command below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Content publishing</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Content receives approval</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Queue item for posting automation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Content owner</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>To be connected when the content folder/platform is provided.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>